--- a/outputs/156-14.xlsx
+++ b/outputs/156-14.xlsx
@@ -141,16 +141,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,73 +410,73 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>99250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>99328</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>209316</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="n">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="n">
         <v>19285.35</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>99329</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>209330</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="n">
         <v>21380.25</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -495,73 +499,73 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>99251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>99500</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>209501</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="n">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="n">
         <v>27350.85</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>99500</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>209501</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="n">
         <v>25915.75</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -584,45 +588,45 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="1" t="n">
         <v>99252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>99500</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>209501</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/outputs/156-14.xlsx
+++ b/outputs/156-14.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="7">
   <si>
     <t xml:space="preserve">Ref</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t xml:space="preserve">Accepted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
   </si>
 </sst>
 </file>
@@ -407,7 +404,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
@@ -468,16 +465,6 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +483,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
@@ -557,16 +544,6 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +562,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="15.63"/>
@@ -614,20 +591,6 @@
       </c>
       <c r="F5" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>99500</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>209501</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
